--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="分账本索引" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="分类与编码" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="命名与查重" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="版本记录" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="3D Prefab总控" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Skill清单" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分账本索引" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -549,7 +549,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="46">
     <border/>
     <border>
       <left style="medium">
@@ -971,11 +971,29 @@
         <color rgb="FFD9E2F3"/>
       </bottom>
     </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF446170"/>
+      </right>
+      <bottom style="medium">
+        <color rgb="FF446170"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF446170"/>
+      </right>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="FF446170"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="396">
+  <cellXfs count="399">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1892,6 +1910,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -2339,16 +2362,16 @@
           <t>条数</t>
         </is>
       </c>
-      <c r="E9" s="320" t="inlineStr">
+      <c r="E9" s="396" t="inlineStr">
         <is>
           <t>AssetID 必须落在归属域的账本里；跨域搬运属跨域变更，须同步本表与 ledger_index.json</t>
         </is>
       </c>
-      <c r="F9" s="125" t="n"/>
-      <c r="G9" s="125" t="n"/>
-      <c r="H9" s="125" t="n"/>
-      <c r="I9" s="125" t="n"/>
-      <c r="J9" s="126" t="n"/>
+      <c r="F9" s="397" t="n"/>
+      <c r="G9" s="397" t="n"/>
+      <c r="H9" s="397" t="n"/>
+      <c r="I9" s="397" t="n"/>
+      <c r="J9" s="398" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="301" t="inlineStr">
@@ -4248,7 +4271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6256,6 +6279,48 @@
       <c r="G58" s="301" t="inlineStr">
         <is>
           <t>摩斯拉</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="46" customHeight="1">
+      <c r="A59" s="301" t="inlineStr">
+        <is>
+          <t>v0.2.1</t>
+        </is>
+      </c>
+      <c r="B59" s="301" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C59" s="301" t="inlineStr">
+        <is>
+          <t>塔楼三层壳体平面统一 100×80m</t>
+        </is>
+      </c>
+      <c r="D59" s="301" t="inlineStr">
+        <is>
+          <t>1个Blend / 1个JSON / 1个GDScript / 1个布局生成脚本 / 3个测试探针</t>
+        </is>
+      </c>
+      <c r="E59" s="301" t="inlineStr">
+        <is>
+          <t>塔楼壳体平面由 18×16 格（90×80m）扩到 20×16 格（100×80m），98F/99F/100F 三层共用同一矩形；原先「90×80 / 250(楼板)160(外墙) / 250」三套口径作废。</t>
+        </is>
+      </c>
+      <c r="F59" s="301" t="inlineStr">
+        <is>
+          <t>不改玩法、数值、刷怪与存档；仅壳体平面与随之重生成的天台装饰布局。AssetID 与 layout_version 不变（原地修正，不新增条目）。</t>
+        </is>
+      </c>
+      <c r="G59" s="301" t="inlineStr">
+        <is>
+          <t>摩斯拉</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>验收：verify_rooftop_32x32_contract / probe_rooftop_parapet_alignment / probe_tower_shell_dimensions / verify_block00_floor98_assembly</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="分账本索引" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="分类与编码" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="命名与查重" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="版本记录" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="3D Prefab总控" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Skill清单" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分账本索引" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="G8" s="85" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="H8" s="85" t="n">
         <v>3</v>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="G8" s="85" t="n">
-        <v>244</v>
+        <v>557</v>
       </c>
       <c r="H8" s="85" t="n">
         <v>3</v>
@@ -5932,16 +5932,16 @@
         </is>
       </c>
       <c r="C5" s="136" t="n">
-        <v>137</v>
+        <v>459</v>
       </c>
       <c r="D5" s="136" t="n">
-        <v>49</v>
+        <v>389</v>
       </c>
       <c r="E5" s="136" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="F5" s="136" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G5" s="137" t="inlineStr">
         <is>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="G8" s="85" t="n">
-        <v>557</v>
+        <v>810</v>
       </c>
       <c r="H8" s="85" t="n">
         <v>3</v>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="C5" s="136" t="n">
-        <v>459</v>
+        <v>712</v>
       </c>
       <c r="D5" s="136" t="n">
-        <v>389</v>
+        <v>641</v>
       </c>
       <c r="E5" s="136" t="n">
         <v>108</v>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="D17" s="85" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E17" s="85" t="n"/>
       <c r="F17" s="85" t="n"/>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="D18" s="85" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18" s="85" t="n"/>
       <c r="F18" s="85" t="n"/>
@@ -6018,20 +6018,20 @@
         </is>
       </c>
       <c r="C7" s="138" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="138" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="139" t="inlineStr">
         <is>
-          <t>桌椅、家具、容器和摆放装饰物</t>
+          <t>桌椅、家具、收音机、容器和摆放装饰物</t>
         </is>
       </c>
       <c r="H7" s="85" t="inlineStr">

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="D11" s="85" t="n">
-        <v>102</v>
+        <v>695</v>
       </c>
       <c r="E11" s="85" t="n"/>
       <c r="F11" s="85" t="n"/>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="G8" s="85" t="n">
-        <v>810</v>
+        <v>829</v>
       </c>
       <c r="H8" s="85" t="n">
         <v>3</v>
@@ -5932,13 +5932,13 @@
         </is>
       </c>
       <c r="C5" s="136" t="n">
-        <v>712</v>
+        <v>722</v>
       </c>
       <c r="D5" s="136" t="n">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="E5" s="136" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F5" s="136" t="n">
         <v>64</v>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分账本索引" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="分账本索引" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="分类与编码" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="命名与查重" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="版本记录" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3D Prefab总控" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Skill清单" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
@@ -1462,7 +1462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="73" min="1" max="2"/>
@@ -1798,21 +1798,21 @@
     <row r="17" ht="15" customHeight="1" s="74">
       <c r="A17" s="86" t="inlineStr">
         <is>
-          <t>角色</t>
+          <t>子弹特效</t>
         </is>
       </c>
       <c r="B17" s="86" t="inlineStr">
         <is>
-          <t>角色</t>
-        </is>
-      </c>
-      <c r="C17" s="85" t="inlineStr">
-        <is>
-          <t>assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx</t>
-        </is>
-      </c>
-      <c r="D17" s="85" t="n">
-        <v>21</v>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="C17" s="86" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_特效账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="D17" s="86" t="n">
+        <v>9</v>
       </c>
       <c r="E17" s="85" t="n"/>
       <c r="F17" s="85" t="n"/>
@@ -1824,17 +1824,17 @@
     <row r="18" ht="15" customHeight="1" s="74">
       <c r="A18" s="86" t="inlineStr">
         <is>
-          <t>道具</t>
+          <t>角色</t>
         </is>
       </c>
       <c r="B18" s="86" t="inlineStr">
         <is>
-          <t>道具</t>
+          <t>角色</t>
         </is>
       </c>
       <c r="C18" s="85" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx</t>
+          <t>assets/registry/ledgers/ShellStorm2_角色账本_v001.xlsx</t>
         </is>
       </c>
       <c r="D18" s="85" t="n">
@@ -1850,21 +1850,21 @@
     <row r="19" ht="15" customHeight="1" s="74">
       <c r="A19" s="86" t="inlineStr">
         <is>
-          <t>音效</t>
+          <t>道具</t>
         </is>
       </c>
       <c r="B19" s="86" t="inlineStr">
         <is>
-          <t>音效</t>
+          <t>道具</t>
         </is>
       </c>
       <c r="C19" s="85" t="inlineStr">
         <is>
-          <t>assets/registry/ledgers/ShellStorm2_音效账本_v001.xlsx</t>
+          <t>assets/registry/ledgers/ShellStorm2_道具账本_v001.xlsx</t>
         </is>
       </c>
       <c r="D19" s="85" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="E19" s="85" t="n"/>
       <c r="F19" s="85" t="n"/>
@@ -1873,31 +1873,57 @@
       <c r="I19" s="85" t="n"/>
       <c r="J19" s="85" t="n"/>
     </row>
-    <row r="20" ht="27.6" customHeight="1" s="74">
-      <c r="A20" s="77" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="74">
+      <c r="A20" s="86" t="inlineStr">
+        <is>
+          <t>音效</t>
+        </is>
+      </c>
+      <c r="B20" s="86" t="inlineStr">
+        <is>
+          <t>音效</t>
+        </is>
+      </c>
+      <c r="C20" s="85" t="inlineStr">
+        <is>
+          <t>assets/registry/ledgers/ShellStorm2_音效账本_v001.xlsx</t>
+        </is>
+      </c>
+      <c r="D20" s="85" t="n">
+        <v>48</v>
+      </c>
+      <c r="E20" s="85" t="n"/>
+      <c r="F20" s="85" t="n"/>
+      <c r="G20" s="85" t="n"/>
+      <c r="H20" s="85" t="n"/>
+      <c r="I20" s="85" t="n"/>
+      <c r="J20" s="85" t="n"/>
+    </row>
+    <row r="21" ht="27.6" customHeight="1" s="74">
+      <c r="A21" s="77" t="inlineStr">
         <is>
           <t>音乐</t>
         </is>
       </c>
-      <c r="B20" s="77" t="inlineStr">
+      <c r="B21" s="77" t="inlineStr">
         <is>
           <t>音乐</t>
         </is>
       </c>
-      <c r="C20" s="87" t="inlineStr">
+      <c r="C21" s="87" t="inlineStr">
         <is>
           <t>assets/registry/ledgers/ShellStorm2_音乐账本_v001.xlsx</t>
         </is>
       </c>
-      <c r="D20" s="77" t="n">
+      <c r="D21" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="E20" s="77" t="n"/>
-      <c r="F20" s="77" t="n"/>
-      <c r="G20" s="77" t="n"/>
-      <c r="H20" s="77" t="n"/>
-      <c r="I20" s="77" t="n"/>
-      <c r="J20" s="77" t="n"/>
+      <c r="E21" s="77" t="n"/>
+      <c r="F21" s="77" t="n"/>
+      <c r="G21" s="77" t="n"/>
+      <c r="H21" s="77" t="n"/>
+      <c r="I21" s="77" t="n"/>
+      <c r="J21" s="77" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2357,11 +2383,11 @@
       </c>
       <c r="D11" s="86" t="inlineStr">
         <is>
-          <t>特效</t>
+          <t>特效 / 子弹特效</t>
         </is>
       </c>
       <c r="E11" s="85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="85" t="inlineStr">
         <is>
@@ -2671,7 +2697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11.94" customWidth="1" style="73" min="1" max="1"/>
@@ -3254,6 +3280,38 @@
       <c r="F16" s="124" t="inlineStr">
         <is>
           <t>BPK-BASE99-ROLLUP-MAIN-DOOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="115" t="inlineStr">
+        <is>
+          <t>VFX</t>
+        </is>
+      </c>
+      <c r="B17" s="115" t="inlineStr">
+        <is>
+          <t>子弹特效</t>
+        </is>
+      </c>
+      <c r="C17" s="115" t="inlineStr">
+        <is>
+          <t>standard / sticky / bounce / piercing / explosive / homing / blackhole / balloon</t>
+        </is>
+      </c>
+      <c r="D17" s="115" t="inlineStr">
+        <is>
+          <t>assets/art/vfx/combat_3d/</t>
+        </is>
+      </c>
+      <c r="E17" s="115" t="inlineStr">
+        <is>
+          <t>vfx_bullet_{type}_root_top3d_v{nnn}.tscn</t>
+        </is>
+      </c>
+      <c r="F17" s="115" t="inlineStr">
+        <is>
+          <t>VFX-BULLET-STANDARD-3D</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.359375" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16.71" customWidth="1" style="73" min="1" max="1"/>
@@ -5776,6 +5834,43 @@
       <c r="G60" s="124" t="inlineStr">
         <is>
           <t>Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="46" customHeight="1" s="74">
+      <c r="A61" s="124" t="inlineStr">
+        <is>
+          <t>v0.2.3</t>
+        </is>
+      </c>
+      <c r="B61" s="124" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C61" s="124" t="inlineStr">
+        <is>
+          <t>新增大类</t>
+        </is>
+      </c>
+      <c r="D61" s="124" t="inlineStr">
+        <is>
+          <t>特效域 / 子弹特效</t>
+        </is>
+      </c>
+      <c r="E61" s="124" t="inlineStr">
+        <is>
+          <t>特效域新增第二大类「子弹特效」，登记 8 个弹种的专属弹体/尾迹/命中特效（均待制作）并把通用弹体 VFX-BULLET-VISUAL-3D 补登进《资产主表》作为其变体父体。同步《分账本索引》特效行（覆盖大类 → 特效 / 子弹特效、大类数 → 2）与《分类与编码》新增 VFX/子弹特效 前缀行。</t>
+        </is>
+      </c>
+      <c r="F61" s="124" t="inlineStr">
+        <is>
+          <t>AssetID、既有 Prefab 路径与运行时行为不变；总目录仍不持有资产行；《总览》新行的「条数」为当前值（9），其余自动作行的条数仍为 2026-09-23 拆分快照。</t>
+        </is>
+      </c>
+      <c r="G61" s="124" t="inlineStr">
+        <is>
+          <t>CodeBuddy</t>
         </is>
       </c>
     </row>

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="分账本索引" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="分类与编码" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="命名与查重" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="版本记录" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="3D Prefab总控" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Skill清单" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分账本索引" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="C9" s="115" t="inlineStr">
         <is>
-          <t>pickup / consumable / key / loot</t>
+          <t>pickup / consumable / key / loot / palette（物品共享色板，assets/art/shared/palette/） / material（物品独立四材质）</t>
         </is>
       </c>
       <c r="D9" s="115" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>biome / room / environment_kit_3d / environment_module_3d / floor / wall / door / stair</t>
+          <t>biome / room / environment_kit_3d / environment_module_3d / floor / wall / door / stair / 远景建筑</t>
         </is>
       </c>
       <c r="D10" s="115" t="inlineStr">

--- a/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
+++ b/assets/registry/ShellStorm2_美术资产台账_v001.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分账本索引" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类与编码" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命名与查重" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本记录" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3D Prefab总控" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill清单" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="分账本索引" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="分类与编码" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="命名与查重" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="版本记录" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3D Prefab总控" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Skill清单" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="G6" s="85" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H6" s="85" t="n">
         <v>1</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="G7" s="85" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H7" s="85" t="n">
         <v>1</v>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="G8" s="85" t="n">
-        <v>829</v>
+        <v>956</v>
       </c>
       <c r="H8" s="85" t="n">
         <v>3</v>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="L8" s="85" t="inlineStr">
         <is>
-          <t>godot-model-asset-import-standard / blender-game-prop-standard / scene-art-merge-into-shared-component</t>
+          <t>02b-godot-model-asset-import-standard / blender-game-prop-standard / scene-art-merge-into-shared-component</t>
         </is>
       </c>
       <c r="M8" s="86" t="inlineStr">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="G9" s="85" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H9" s="85" t="n">
         <v>2</v>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G11" s="85" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H11" s="85" t="n">
         <v>1</v>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="L11" s="85" t="inlineStr">
         <is>
-          <t>godot-model-asset-import-standard</t>
+          <t>02b-godot-model-asset-import-standard</t>
         </is>
       </c>
       <c r="M11" s="86" t="inlineStr">
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="G12" s="85" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H12" s="85" t="n">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="G13" s="91" t="n">
-        <v>48</v>
+        <v>152</v>
       </c>
       <c r="H13" s="91" t="n">
         <v>0</v>
@@ -2662,7 +2662,7 @@
     <row r="17" ht="15" customHeight="1" s="74">
       <c r="A17" s="102" t="inlineStr">
         <is>
-          <t>快照日期 2026-09-23；条数为当前运行时真源对账后的快照，权威数量在各分账本《总览》。新增资产先确认归属域，再进对应分账本登记。</t>
+          <t>快照日期 2026-10-16；条数为当前运行时真源对账后的快照（合计 1,287 项），权威数量在各分账本《总览》。新增资产先确认归属域，再进对应分账本登记。</t>
         </is>
       </c>
       <c r="B17" s="103" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="D5" s="147" t="inlineStr">
         <is>
-          <t>/Users/summercards/.codex/skills/shellstorm-art-assets/SKILL.md</t>
+          <t>.codex/skills/shellstorm2-asset-ledger-row-authoring/SKILL.md</t>
         </is>
       </c>
       <c r="E5" s="148" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="D7" s="147" t="inlineStr">
         <is>
-          <t>.codex/skills/godot-model-asset-import-standard/SKILL.md</t>
+          <t>.codex/skills/02b-godot-model-asset-import-standard/SKILL.md</t>
         </is>
       </c>
       <c r="E7" s="148" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="D8" s="147" t="inlineStr">
         <is>
-          <t>skills_drafts/player-avatar-asset-standard/SKILL.md</t>
+          <t>.codex/skills/player-avatar-asset-standard/SKILL.md</t>
         </is>
       </c>
       <c r="E8" s="148" t="inlineStr">
         <is>
-          <t>未安装（项目草稿）</t>
+          <t>项目内已安装</t>
         </is>
       </c>
       <c r="F8" s="148" t="inlineStr">
